--- a/onepop_數學橫幅_全冊.xlsx
+++ b/onepop_數學橫幅_全冊.xlsx
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ch5 機率</t>
+          <t>Ch6 機率</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
